--- a/TESTS/zlit_5_farb_shakal.xlsx
+++ b/TESTS/zlit_5_farb_shakal.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -603,6 +608,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -645,6 +655,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -687,6 +702,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Посланцем богів — Кокаліко — якого послав сам Брахма правити всіма звірами</t>
+          <t>Посланцем богів</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -771,6 +796,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Знаком обраності від богів — мовляв, боги самі пофарбували його і призначили правителем</t>
+          <t>Знаком обраності від богів</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -855,6 +890,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -939,6 +984,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Чому шакал того дня тікав від собак до самого міста?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він заблукав</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зголоднілий, він забіг у місто шукати їжу, і його погнали собаки</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він шукав друзів</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він хотів подивитись на людей</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Де саме стояла діжка із синьою фарбою, в яку впав шакал?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У лісі</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>На подвір'ї фарбувальника, серед інших чанів із фарбою</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У річці</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>На ринку</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Що сталося із собаками, коли шакал вискочив із синьою шкірою?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони впізнали його і продовжили гнатися</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони злякались незнайомого синього звіра і розбіглись</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони засміялись</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони побігли за фарбувальником</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Як шакал вирішив скористатися своїм новим виглядом?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сховатися назавжди в норі</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вийти до тварин лісу і скористатися їхнім страхом перед невідомим</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Піти жити у місто</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Знайти фарбувальника і подякувати</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що подумав шакал, коли вперше побачив своє синє відображення у воді?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Що йому потрібно змити фарбу</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Що такого незвичайного кольору варто скористатися, поки інші бояться його</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що він захворів</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Що тепер його ніхто не впізнає і це погано</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Чому шакал обрав саме роль «царя», а не просто незвичайної тварини?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо так йому наказали боги</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо влада над іншими дала б йому їжу й безпеку без зусиль</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо він завжди мріяв про трон</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо інші тварини самі попросили його стати царем</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Як пофарбований шакал організував своє «правління» серед тварин?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він нічого не змінював</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Призначив левів, тигрів та вовків своїми «міністрами» й охороною</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він жив окремо від усіх</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він улаштував свято для всіх</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Чому навіть лев і тигр, сильніші за шакала, підкорилися йому?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він їх переміг у бою</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони повірили в його «божественне» походження через незвичайний колір</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він їм заплатив</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він був хитрішим мисливцем</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що отримував сам шакал від такого «правління», поки тварини йому служили?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого, лише повагу</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Найкращу їжу, яку приносили йому щодня без жодних зусиль з його боку</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Золото і коштовності</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Право будувати палаци</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Що сталося одного вечора, коли десь далеко завили інші шакали?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ніхто цього не почув</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У «царя» прокинувся природний інстинкт, і він мимоволі почав вити у відповідь</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лев одразу пішов перевірити</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Тварини почали танцювати</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Чому саме виття стало проблемою для пофарбованого шакала?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Воно було занадто тихим</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Усі тварини добре знали, що так кричать саме шакали, а не «посланці богів»</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Воно налякало левів</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Воно привернуло мисливців</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Як змінилися обличчя тварин одразу після того, як прозвучало виття «царя»?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не змінилось</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Здивування швидко перетворилося на гнів, коли всі зрозуміли обман</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони засміялись із жалю</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони злякались ще більше</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що тварини зробили, щойно зрозуміли, що «цар» — це звичайний шакал?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Продовжили йому служити з остраху</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Накинулися на нього, щоб покарати за обман</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Влаштували суд</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Попросили вибачення у нього</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Що шакалу вдалося зробити в останній момент, коли тварини кинулись на нього?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він став невидимим</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він утік і сховався в найближчій печері</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він перетворився назад на «царя»</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він покликав на допомогу левів</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Чи повернулась колишня шана тварин до шакала після викриття?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Так, вони пробачили його</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ні, він остаточно втратив будь-яку повагу і повернувся до звичайного життя</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Так, частково</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Невідомо, казка не каже</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>На яких людей у житті, за змістом казки, схожий пофарбований шакал?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>На щирих лідерів</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>На тих, хто здобуває владу обманом, видаючи себе за більшого, ніж є насправді</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>На простих працівників</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>На мандрівників</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Чому тварини, що підкорялися шакалу, теж виглядають комічно в очах читача?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо вони злі</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо їхня покора заснована лише на зовнішньому вигляді, а не на перевірених фактах</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо вони слабкі фізично</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо вони самі хотіли обманювати</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Чого, за змістом казки, варто остерігатися, дивлячись на «незвичайних» правителів?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Їхнього багатства</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Того, що зовнішня незвичайність — ще не доказ величі чи права керувати</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Їхньої молодості</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Їхньої доброти</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>До якого жанру належить «Фарбований шакал»?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Роман</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Алегорична казка-притча з тваринами-персонажами</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вірш</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Драма</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Чому саме тварини, а не люди, є героями такої казки-притчі?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо казки про людей заборонені</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Через образи тварин зручно й безпечно показувати людські вади та повчати</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо тварин легше малювати</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо так коротше</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Який настрій переважає в кінці казки «Фарбований шакал»?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сумний і трагічний</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Викривальний і трохи повчально-комічний — обман отримав заслужену відплату</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Страшний</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Романтичний</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>До якої країни належить ця народна казка?</t>
+          <t>«Фарбований шакал» — індійська народна казка-притча.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>З яким збірником пов'язують казку «Фарбований шакал»?</t>
+          <t>Подібні казки-притчі про тварин часто пов'язують зі збіркою «Панчатантра».</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Що таке «Панчатантра» у зв'язку з цією казкою?</t>
+          <t>«Панчатантра» — це збірка повчальних оповідань і притч, де героями є тварини.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,29 +2207,32 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Чим закінчилась казка для шакала після викриття?</t>
+          <t>Після викриття шакал був прощений і залишився «царем» назавжди.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка головна мораль казки «Фарбований шакал»?</t>
+          <t>Головна мораль казки — обман і самозванство неминуче будуть викриті.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Який урок несе ця казка читачам?</t>
+          <t>Казка вчить, що зовнішній вигляд важливіший за справжню сутність і вчинки.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,37 +2412,42 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які риси характеру шакала розкриває ця казка?</t>
+          <t>Що зрештою сталося із пофарбованим шакалом?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Хитрість і брехливість</t>
+          <t>Його викрило власне виття</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Сміливість</t>
+          <t>Тварини кинулись на нього, і він утік</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Самозванство і гордість</t>
+          <t>Він став справжнім царем лісу</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Доброта</t>
+          <t>Він повернувся до звичайного життя шакала</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>А,В</t>
+          <t>А,Б,Г</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2295,6 +2492,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2337,6 +2539,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Він не втримався і завив по-шакальячи почувши родичів — інстинкт переміг брехню</t>
+          <t>Він не втримався і завив по-шакальячи почувши родичів</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
